--- a/site/Watchdog-Setup-Guide-ADP-Workforce-Now-Okta-ServiceNow-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-ADP-Workforce-Now-Okta-ServiceNow-Integration/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,28 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ITSM Dashboards Created by Watchdog</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KWKCJSCJ2G3JW6BD2DB3S7PN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Watchdog-Setup-Guide-ADP-Workforce-Now-Okta-ServiceNow-Integration/#h_01KWKCJSCJ2G3JW6BD2DB3S7PN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Watchdog-Setup-Guide-ADP-Workforce-Now-Okta-ServiceNow-Integration/headings.xlsx
+++ b/site/Watchdog-Setup-Guide-ADP-Workforce-Now-Okta-ServiceNow-Integration/headings.xlsx
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Directory Policy</t>
+          <t>Directory Access Policy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
